--- a/artfynd/A 53312-2023 artfynd.xlsx
+++ b/artfynd/A 53312-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53312-2023 artfynd.xlsx
+++ b/artfynd/A 53312-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111899547</v>
+        <v>111899453</v>
       </c>
       <c r="B12" t="n">
-        <v>86297</v>
+        <v>90857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,25 +1892,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4379</v>
+        <v>5448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallskog med inslag av lövträd; vägkant</t>
+          <t>Tallskog med inslag av lövträd</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111899453</v>
+        <v>117355503</v>
       </c>
       <c r="B13" t="n">
-        <v>90857</v>
+        <v>97836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,44 +2003,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Skiren N, Ög</t>
+          <t>Ormlången, Lotorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546745</v>
+        <v>546726</v>
       </c>
       <c r="R13" t="n">
-        <v>6513996</v>
+        <v>6514437</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2064,12 +2065,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,130 +2083,18 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallskog med inslag av lövträd</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Joakim Isaksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Joakim Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>117355503</v>
-      </c>
-      <c r="B14" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ormlången, Lotorp, Ög</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>546726</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6514437</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Joakim Isaksson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Joakim Isaksson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
